--- a/ncxlxs/pack__ncxlsx__튜토리얼.xlsx
+++ b/ncxlxs/pack__ncxlsx__튜토리얼.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1115,7 +1115,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1000"/>
   </ignoredErrors>
 </worksheet>
 </file>